--- a/Docs/Integracion Estructura DBIsam  -  SQLite SoperacionInv-01.xlsx
+++ b/Docs/Integracion Estructura DBIsam  -  SQLite SoperacionInv-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desarrollos\MyPython\Tkinter\ArkConInv\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2C4269-4E48-4165-B02D-02437FDF6259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633B11DC-9131-4485-AB66-A20E3515A7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1118,7 +1118,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1298,6 +1298,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1459,7 +1465,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1468,6 +1474,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2419,7 +2426,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -2474,7 +2481,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -3024,7 +3031,7 @@
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="4" t="s">
         <v>126</v>
       </c>
       <c r="B109" s="1" t="s">
